--- a/backend/medical-registry/src/main/resources/MedicalRegistryImportTemplate.xlsx
+++ b/backend/medical-registry/src/main/resources/MedicalRegistryImportTemplate.xlsx
@@ -36,8 +36,7 @@
     </comment>
     <comment ref="D1" authorId="0">
       <text>
-        <t>Pflichtfeld
-Länge zwischen 1 und 40 Zeichen</t>
+        <t>Länge zwischen 1 und 40 Zeichen</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
@@ -96,8 +95,7 @@
     </comment>
     <comment ref="N1" authorId="0">
       <text>
-        <t>Pflichtfeld
-EmailAddressConstraint</t>
+        <t>EmailAddressConstraint</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0">
@@ -179,7 +177,7 @@
     <comment ref="AF1" authorId="0">
       <text>
         <t>bedingtes Pflichtfeld
-EmailAddressConstraint</t>
+MandatoryEmailAddressConstraint</t>
       </text>
     </comment>
     <comment ref="AG1" authorId="0">

--- a/backend/medical-registry/src/main/resources/MedicalRegistryImportTemplate.xlsx
+++ b/backend/medical-registry/src/main/resources/MedicalRegistryImportTemplate.xlsx
@@ -24,13 +24,13 @@
     </comment>
     <comment ref="B1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 120 Zeichen</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 80 Zeichen</t>
       </text>
     </comment>
@@ -41,55 +41,55 @@
     </comment>
     <comment ref="E1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 55 Zeichen</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 11 Zeichen</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 20 Zeichen</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 50 Zeichen</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
-        <t>Pflichtfeld
-Erlaubte Werte: AD,AE,AF,AG,AI,AL,AM,AO,AQ,AR,AS,AT,AU,AW,AX,AZ,BA,BB,BD,BE,BF,BG,BH,BI,BJ,BL,BM,BN,BO,BQ,BR,BS,BT,BV,BW,BY,BZ,CA,CC,CD,CF,CG,CH,CI,CK,CL,CM,CN,CO,CR,CU,CV,CW,CX,CY,CZ,DE,DJ,DK,DM,DO,DZ,EC,EE,EG,EH,ER,ES,ET,FI,FJ,FK,FM,FO,FR,GA,GB,GD,GE,GF,GG,GH,GI,GL,GM,GN,GP,GQ,GR,GS,GT,GU,GW,GY,HK,HM,HN,HR,HT,HU,ID,IE,IL,IM,IN,IO,IQ,IR,IS,IT,JE,JM,JO,JP,KE,KG,KH,KI,KM,KN,KP,KR,KW,KY,KZ,LA,LB,LC,LI,LK,LR,LS,LT,LU,LV,LY,MA,MC,MD,ME,MF,MG,MH,MK,ML,MM,MN,MO,MP,MQ,MR,MS,MT,MU,MV,MW,MX,MY,MZ,NA,NC,NE,NF,NG,NI,NL,NO,NP,NR,NU,NZ,OM,PA,PE,PF,PG,PH,PK,PL,PM,PN,PR,PS,PT,PW,PY,QA,RE,RO,RS,RU,RW,SA,SB,SC,SD,SE,SG,SH,SI,SJ,SK,SL,SM,SN,SO,SR,SS,ST,SV,SX,SY,SZ,TC,TD,TF,TG,TH,TJ,TK,TL,TM,TN,TO,TR,TT,TV,TW,TZ,UA,UG,UM,US,UY,UZ,VA,VC,VE,VG,VI,VN,VU,WF,WS,YE,YT,ZA,ZM,ZW</t>
+        <t>Pflichtfeld
+Erlaubte Werte: AD,AE,AF,AG,AI,AL,AM,AO,AQ,AR,AS,AT,AU,AW,AX,AZ,BA,BB,BD,BE,BF,BG,BH,BI,BJ,BL,BM,BN,BO,BQ,BR,BS,BT,BV,BW,BY,BZ,CA,CC,CD,CF,CG,CH,CI,CK,CL,CM,CN,CO,CR,CU,CV,CW,CX,CY,CZ,DE,DJ,DK,DM,DO,DZ,EC,EE,EG,EH,ER,ES,ET,FI,FJ,FK,FM,FO,FR,GA,GB,GD,GE,GF,GG,GH,GI,GL,GM,GN,GP,GQ,GR,GS,GT,GU,GW,GY,HK,HM,HN,HR,HT,HU,ID,IE,IL,IM,IN,IO,IQ,IR,IS,IT,JE,JM,JO,JP,KE,KG,KH,KI,KM,KN,KP,KR,KW,KY,KZ,LA,LB,LC,LI,LK,LR,LS,LT,LU,LV,LY,MA,MC,MD,ME,MF,MG,MH,MK,ML,MM,MN,MO,MP,MQ,MR,MS,MT,MU,MV,MW,MX,MY,MZ,NA,NC,NE,NF,NG,NI,NL,NO,NP,NR,NU,NZ,OM,PA,PE,PF,PG,PH,PK,PL,PM,PN,PR,PS,PT,PW,PY,QA,RE,RO,RS,RU,RW,SA,SB,SC,SD,SE,SG,SH,SI,SJ,SK,SL,SM,SN,SO,SR,SS,ST,SV,SX,SY,SZ,TC,TD,TF,TG,TH,TJ,TK,TL,TM,TN,TO,TR,TT,TV,TW,TZ,UA,UG,UM,US,UY,UZ,VA,VC,VE,VG,VI,VN,VU,WF,WS,YE,YT,ZA,ZM,ZW,XK,UNKNOWN,STATELESS</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Datum (Bsp: 31.01.2000)</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 50 Zeichen</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0">
       <text>
-        <t>Pflichtfeld
-Erlaubte Werte: AD,AE,AF,AG,AI,AL,AM,AO,AQ,AR,AS,AT,AU,AW,AX,AZ,BA,BB,BD,BE,BF,BG,BH,BI,BJ,BL,BM,BN,BO,BQ,BR,BS,BT,BV,BW,BY,BZ,CA,CC,CD,CF,CG,CH,CI,CK,CL,CM,CN,CO,CR,CU,CV,CW,CX,CY,CZ,DE,DJ,DK,DM,DO,DZ,EC,EE,EG,EH,ER,ES,ET,FI,FJ,FK,FM,FO,FR,GA,GB,GD,GE,GF,GG,GH,GI,GL,GM,GN,GP,GQ,GR,GS,GT,GU,GW,GY,HK,HM,HN,HR,HT,HU,ID,IE,IL,IM,IN,IO,IQ,IR,IS,IT,JE,JM,JO,JP,KE,KG,KH,KI,KM,KN,KP,KR,KW,KY,KZ,LA,LB,LC,LI,LK,LR,LS,LT,LU,LV,LY,MA,MC,MD,ME,MF,MG,MH,MK,ML,MM,MN,MO,MP,MQ,MR,MS,MT,MU,MV,MW,MX,MY,MZ,NA,NC,NE,NF,NG,NI,NL,NO,NP,NR,NU,NZ,OM,PA,PE,PF,PG,PH,PK,PL,PM,PN,PR,PS,PT,PW,PY,QA,RE,RO,RS,RU,RW,SA,SB,SC,SD,SE,SG,SH,SI,SJ,SK,SL,SM,SN,SO,SR,SS,ST,SV,SX,SY,SZ,TC,TD,TF,TG,TH,TJ,TK,TL,TM,TN,TO,TR,TT,TV,TW,TZ,UA,UG,UM,US,UY,UZ,VA,VC,VE,VG,VI,VN,VU,WF,WS,YE,YT,ZA,ZM,ZW</t>
+        <t>Pflichtfeld
+Erlaubte Werte: AD,AE,AF,AG,AI,AL,AM,AO,AQ,AR,AS,AT,AU,AW,AX,AZ,BA,BB,BD,BE,BF,BG,BH,BI,BJ,BL,BM,BN,BO,BQ,BR,BS,BT,BV,BW,BY,BZ,CA,CC,CD,CF,CG,CH,CI,CK,CL,CM,CN,CO,CR,CU,CV,CW,CX,CY,CZ,DE,DJ,DK,DM,DO,DZ,EC,EE,EG,EH,ER,ES,ET,FI,FJ,FK,FM,FO,FR,GA,GB,GD,GE,GF,GG,GH,GI,GL,GM,GN,GP,GQ,GR,GS,GT,GU,GW,GY,HK,HM,HN,HR,HT,HU,ID,IE,IL,IM,IN,IO,IQ,IR,IS,IT,JE,JM,JO,JP,KE,KG,KH,KI,KM,KN,KP,KR,KW,KY,KZ,LA,LB,LC,LI,LK,LR,LS,LT,LU,LV,LY,MA,MC,MD,ME,MF,MG,MH,MK,ML,MM,MN,MO,MP,MQ,MR,MS,MT,MU,MV,MW,MX,MY,MZ,NA,NC,NE,NF,NG,NI,NL,NO,NP,NR,NU,NZ,OM,PA,PE,PF,PG,PH,PK,PL,PM,PN,PR,PS,PT,PW,PY,QA,RE,RO,RS,RU,RW,SA,SB,SC,SD,SE,SG,SH,SI,SJ,SK,SL,SM,SN,SO,SR,SS,ST,SV,SX,SY,SZ,TC,TD,TF,TG,TH,TJ,TK,TL,TM,TN,TO,TR,TT,TV,TW,TZ,UA,UG,UM,US,UY,UZ,VA,VC,VE,VG,VI,VN,VU,WF,WS,YE,YT,ZA,ZM,ZW,XK,UNKNOWN,STATELESS</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 23 Zeichen</t>
       </text>
     </comment>
@@ -100,13 +100,13 @@
     </comment>
     <comment ref="O1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: NOT_SPECIFIED,DIVERSE,FEMALE,MALE</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: DOCTOR,DENTIST,PSYCHOLOGICAL_PSYCHOTHERAPIST,NURSING_ASSISTANT,GERIATRIC_NURSE,DIETICIAN,DISINFECTOR,OCCUPATIONAL_THERAPIST,HEALTH_SUPERVISOR,HEALTHCARE_AND_PEDIATRIC_NURSE,HEALTHCARE_AND_NURSING_ASSISTANT,HEALTHCARE_AND_NURSING_ASSISTANTS_HELPER,MIDWIVE_MATERNITY_NURSE,ALTERNATIVE_PRACTITIONER,NON_MEDICAL_PRACTITIONER_FOR_CHIROPRACTIC,ALTERNATIVE_PRACTITIONER_FOR_SPEECH_THERAPY,NON_MEDICAL_PRACTITIONER_FOR_PHYSIOTHERAPY,NON_MEDICAL_PRACTITIONER_FOR_PSYCHOTHERAPY,CHILD_AND_YOUTH_PSYCHOTHERAPIST,SPEECH_THERAPIST,MASSEUR_AND_MEDICAL_BATH_ATTENDANT,MEDICAL_DOCUMENTALIST,MEDICAL_TECHNICAL_LABORATORY_ASSISTANT,MEDICAL_TECHNICAL_RADIOLOGY_ASSISTANT,MEDICAL_TECHNICAL_ASSISTANT_FOR_FUNCTIONAL_DIAGNOSTICS,EMERGENCY_PARAMEDIC,ORTHOPTIST,CARE_ASSISTANT,NURSING_SERVICE,NURSING_SERVICE_MANAGER,PHARMACEUTICAL_TECHNICAL_ASSISTANT,PHYSIOTHERAPIST,PODIATRIST,RADIOLOGY_ASSISTANT,SPORTS_THERAPIST,PHARMACIST,VETERINARIAN</t>
       </text>
     </comment>
@@ -117,7 +117,7 @@
     </comment>
     <comment ref="V1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Datum (Bsp: 31.01.2000)</t>
       </text>
     </comment>
@@ -128,55 +128,55 @@
     </comment>
     <comment ref="X1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: FULL_TIME,PART_TIME</t>
       </text>
     </comment>
     <comment ref="Y1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: SELF_EMPLOYED,FREELANCE,EMPLOYEE</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 300 Zeichen</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 55 Zeichen</t>
       </text>
     </comment>
     <comment ref="AB1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 11 Zeichen</t>
       </text>
     </comment>
     <comment ref="AC1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 20 Zeichen</t>
       </text>
     </comment>
     <comment ref="AD1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 50 Zeichen</t>
       </text>
     </comment>
     <comment ref="AE1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 23 Zeichen</t>
       </text>
     </comment>
     <comment ref="AF1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 MandatoryEmailAddressConstraint</t>
       </text>
     </comment>
@@ -197,14 +197,14 @@
     </comment>
     <comment ref="AK1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Erlaubte Werte: JA,NEIN</t>
       </text>
     </comment>
     <comment ref="AL1" authorId="0">
       <text>
-        <t>Pflichtfeld
-Pflichtfeld
+        <t>Pflichtfeld
+Pflichtfeld
 Erlaubte Werte: JA,NEIN</t>
       </text>
     </comment>

--- a/backend/medical-registry/src/main/resources/MedicalRegistryImportTemplate.xlsx
+++ b/backend/medical-registry/src/main/resources/MedicalRegistryImportTemplate.xlsx
@@ -24,13 +24,13 @@
     </comment>
     <comment ref="B1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 120 Zeichen</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 80 Zeichen</t>
       </text>
     </comment>
@@ -41,55 +41,56 @@
     </comment>
     <comment ref="E1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 55 Zeichen</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 11 Zeichen</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 20 Zeichen</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 50 Zeichen</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: AD,AE,AF,AG,AI,AL,AM,AO,AQ,AR,AS,AT,AU,AW,AX,AZ,BA,BB,BD,BE,BF,BG,BH,BI,BJ,BL,BM,BN,BO,BQ,BR,BS,BT,BV,BW,BY,BZ,CA,CC,CD,CF,CG,CH,CI,CK,CL,CM,CN,CO,CR,CU,CV,CW,CX,CY,CZ,DE,DJ,DK,DM,DO,DZ,EC,EE,EG,EH,ER,ES,ET,FI,FJ,FK,FM,FO,FR,GA,GB,GD,GE,GF,GG,GH,GI,GL,GM,GN,GP,GQ,GR,GS,GT,GU,GW,GY,HK,HM,HN,HR,HT,HU,ID,IE,IL,IM,IN,IO,IQ,IR,IS,IT,JE,JM,JO,JP,KE,KG,KH,KI,KM,KN,KP,KR,KW,KY,KZ,LA,LB,LC,LI,LK,LR,LS,LT,LU,LV,LY,MA,MC,MD,ME,MF,MG,MH,MK,ML,MM,MN,MO,MP,MQ,MR,MS,MT,MU,MV,MW,MX,MY,MZ,NA,NC,NE,NF,NG,NI,NL,NO,NP,NR,NU,NZ,OM,PA,PE,PF,PG,PH,PK,PL,PM,PN,PR,PS,PT,PW,PY,QA,RE,RO,RS,RU,RW,SA,SB,SC,SD,SE,SG,SH,SI,SJ,SK,SL,SM,SN,SO,SR,SS,ST,SV,SX,SY,SZ,TC,TD,TF,TG,TH,TJ,TK,TL,TM,TN,TO,TR,TT,TV,TW,TZ,UA,UG,UM,US,UY,UZ,VA,VC,VE,VG,VI,VN,VU,WF,WS,YE,YT,ZA,ZM,ZW,XK,UNKNOWN,STATELESS</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
+DateOfBirth
 Datum (Bsp: 31.01.2000)</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 50 Zeichen</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: AD,AE,AF,AG,AI,AL,AM,AO,AQ,AR,AS,AT,AU,AW,AX,AZ,BA,BB,BD,BE,BF,BG,BH,BI,BJ,BL,BM,BN,BO,BQ,BR,BS,BT,BV,BW,BY,BZ,CA,CC,CD,CF,CG,CH,CI,CK,CL,CM,CN,CO,CR,CU,CV,CW,CX,CY,CZ,DE,DJ,DK,DM,DO,DZ,EC,EE,EG,EH,ER,ES,ET,FI,FJ,FK,FM,FO,FR,GA,GB,GD,GE,GF,GG,GH,GI,GL,GM,GN,GP,GQ,GR,GS,GT,GU,GW,GY,HK,HM,HN,HR,HT,HU,ID,IE,IL,IM,IN,IO,IQ,IR,IS,IT,JE,JM,JO,JP,KE,KG,KH,KI,KM,KN,KP,KR,KW,KY,KZ,LA,LB,LC,LI,LK,LR,LS,LT,LU,LV,LY,MA,MC,MD,ME,MF,MG,MH,MK,ML,MM,MN,MO,MP,MQ,MR,MS,MT,MU,MV,MW,MX,MY,MZ,NA,NC,NE,NF,NG,NI,NL,NO,NP,NR,NU,NZ,OM,PA,PE,PF,PG,PH,PK,PL,PM,PN,PR,PS,PT,PW,PY,QA,RE,RO,RS,RU,RW,SA,SB,SC,SD,SE,SG,SH,SI,SJ,SK,SL,SM,SN,SO,SR,SS,ST,SV,SX,SY,SZ,TC,TD,TF,TG,TH,TJ,TK,TL,TM,TN,TO,TR,TT,TV,TW,TZ,UA,UG,UM,US,UY,UZ,VA,VC,VE,VG,VI,VN,VU,WF,WS,YE,YT,ZA,ZM,ZW,XK,UNKNOWN,STATELESS</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Länge zwischen 1 und 23 Zeichen</t>
       </text>
     </comment>
@@ -100,13 +101,13 @@
     </comment>
     <comment ref="O1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: NOT_SPECIFIED,DIVERSE,FEMALE,MALE</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: DOCTOR,DENTIST,PSYCHOLOGICAL_PSYCHOTHERAPIST,NURSING_ASSISTANT,GERIATRIC_NURSE,DIETICIAN,DISINFECTOR,OCCUPATIONAL_THERAPIST,HEALTH_SUPERVISOR,HEALTHCARE_AND_PEDIATRIC_NURSE,HEALTHCARE_AND_NURSING_ASSISTANT,HEALTHCARE_AND_NURSING_ASSISTANTS_HELPER,MIDWIVE_MATERNITY_NURSE,ALTERNATIVE_PRACTITIONER,NON_MEDICAL_PRACTITIONER_FOR_CHIROPRACTIC,ALTERNATIVE_PRACTITIONER_FOR_SPEECH_THERAPY,NON_MEDICAL_PRACTITIONER_FOR_PHYSIOTHERAPY,NON_MEDICAL_PRACTITIONER_FOR_PSYCHOTHERAPY,CHILD_AND_YOUTH_PSYCHOTHERAPIST,SPEECH_THERAPIST,MASSEUR_AND_MEDICAL_BATH_ATTENDANT,MEDICAL_DOCUMENTALIST,MEDICAL_TECHNICAL_LABORATORY_ASSISTANT,MEDICAL_TECHNICAL_RADIOLOGY_ASSISTANT,MEDICAL_TECHNICAL_ASSISTANT_FOR_FUNCTIONAL_DIAGNOSTICS,EMERGENCY_PARAMEDIC,ORTHOPTIST,CARE_ASSISTANT,NURSING_SERVICE,NURSING_SERVICE_MANAGER,PHARMACEUTICAL_TECHNICAL_ASSISTANT,PHYSIOTHERAPIST,PODIATRIST,RADIOLOGY_ASSISTANT,SPORTS_THERAPIST,PHARMACIST,VETERINARIAN</t>
       </text>
     </comment>
@@ -117,7 +118,7 @@
     </comment>
     <comment ref="V1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Datum (Bsp: 31.01.2000)</t>
       </text>
     </comment>
@@ -128,55 +129,55 @@
     </comment>
     <comment ref="X1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: FULL_TIME,PART_TIME</t>
       </text>
     </comment>
     <comment ref="Y1" authorId="0">
       <text>
-        <t>Pflichtfeld
+        <t>Pflichtfeld
 Erlaubte Werte: SELF_EMPLOYED,FREELANCE,EMPLOYEE</t>
       </text>
     </comment>
     <comment ref="Z1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 300 Zeichen</t>
       </text>
     </comment>
     <comment ref="AA1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 55 Zeichen</t>
       </text>
     </comment>
     <comment ref="AB1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 11 Zeichen</t>
       </text>
     </comment>
     <comment ref="AC1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 20 Zeichen</t>
       </text>
     </comment>
     <comment ref="AD1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 50 Zeichen</t>
       </text>
     </comment>
     <comment ref="AE1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Länge zwischen 1 und 23 Zeichen</t>
       </text>
     </comment>
     <comment ref="AF1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 MandatoryEmailAddressConstraint</t>
       </text>
     </comment>
@@ -197,14 +198,14 @@
     </comment>
     <comment ref="AK1" authorId="0">
       <text>
-        <t>bedingtes Pflichtfeld
+        <t>bedingtes Pflichtfeld
 Erlaubte Werte: JA,NEIN</t>
       </text>
     </comment>
     <comment ref="AL1" authorId="0">
       <text>
-        <t>Pflichtfeld
-Pflichtfeld
+        <t>Pflichtfeld
+Pflichtfeld
 Erlaubte Werte: JA,NEIN</t>
       </text>
     </comment>
